--- a/frontend/e2e/fixtures/teachers_with_account.xlsx
+++ b/frontend/e2e/fixtures/teachers_with_account.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>身分末四碼</t>
+          <t>证件后四位</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,17 +434,17 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>基本鐘點</t>
+          <t>基本课时</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>行政職稱</t>
+          <t>行政职务</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>行政減課</t>
+          <t>行政减课</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>登入帳號</t>
+          <t>登录账号</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,133 +464,133 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>手機</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>LINE ID</t>
+          <t>即时通讯账号</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>說明</t>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>陳老師</t>
+          <t>陈老师</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>chen@example.edu.tw</t>
+          <t>chen@example.edu.cn</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
